--- a/Ket_Qua_Phan_Tich_SO SÁNH PP - ĐTCS/2. TLTK_ĐTCS2.xlsx
+++ b/Ket_Qua_Phan_Tich_SO SÁNH PP - ĐTCS/2. TLTK_ĐTCS2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Tổng quan</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>ước tính tỷ lệ rủi ro gộp (RR) và sự khác biệt trung bình chuẩn hóa (SMD) bằng cách sử dụng mô hình hiệu ứng ngẫu nhiên</t>
-  </si>
-  <si>
-    <t>Phản hồi áp suất đo được với nguyên mẫu này phù hợp tốt với các mô phỏng, với sai số bình phương trung bình &lt;5,2%</t>
   </si>
   <si>
     <t>Effects of a pneumatic tube system on the hemolysis of blood samples: a PRISMA-compliant meta-analysis</t>
@@ -85,14 +82,320 @@
     <t>https://www.sciencedirect.com/science/article/pii/S2352551717300239</t>
   </si>
   <si>
-    <r>
-      <t>median values of chemistry parameters were not significantly different except for AST (</t>
-    </r>
-    <r>
-      <rPr>
+    <t>KQ1 ảnh hưởng chỉ số tan máu</t>
+  </si>
+  <si>
+    <t>KQ2 ảnh hưởng chỉ số hóa sinh</t>
+  </si>
+  <si>
+    <t>không tìm thấy tác động đáng kể của PTS lên hiện tượng tan máu đã được khẳng định thêm bằng việc không có sự khác biệt rõ rệt nào giữa các hợp chất hồng cầu như K, ALT và AST giữa các mẫu được vận chuyển bằng PTS hoặc bằng tay. Tương tự, Pupek et al. [Trích dẫn28 ] tin rằng việc sử dụng PTS không ảnh hưởng đến nồng độ K, ALT và AST trong mẫu máu. Kapoula et al. [Trích dẫn23 ] cũng báo cáo rằng phương thức vận chuyển không có tác động đáng kể đến các thông số huyết thanh đo được như nồng độ K và AST. Tuy nhiên, phân tích tổng hợp do Kapoula et al. thực hiện [Trích dẫn9 ] đã mang lại kết quả có ý nghĩa thống kê đối với K và AST. Các nguyên nhân có thể dẫn đến sự khác biệt này như sau: (1) các mẫu máu được phân tích trong nghiên cứu của họ được lấy từ một quy trình chọc tĩnh mạch duy nhất, nhưng các giá trị cơ bản cho các mẫu máu ghép đôi được phân tích song song là tương đương, và chúng cũng được đưa vào nghiên cứu của chúng tôi; (2) Kapoula et al. đã sử dụng sự khác biệt trung bình làm kích thước hiệu ứng, khác với việc chúng tôi sử dụng SMD; và (3) cuối cùng, phân tích tổng hợp của chúng tôi gần đây hơn và bao gồm nhiều bài báo tạp chí hơn so với của Kapoula et al.</t>
+  </si>
+  <si>
+    <r>
+      <t>Một phát hiện đặc biệt thú vị trong nghiên cứu của chúng tôi là các mẫu máu được vận chuyển bằng hệ thống PTS có nồng độ LDH cao hơn so với các mẫu được vận chuyển thủ công (với khoảng tin cậy 95% từ 0,06 đến 0,34). Chúng tôi nghi ngờ rằng chỉ có LDH từ các mẫu được vận chuyển bằng hệ thống PTS cho thấy sự khác biệt đáng kể do nồng độ LDH cao hơn ngưỡng nhạy cảm của xét nghiệm.</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FF10147E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trích dẫn35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> ]. Nồng độ LDH trong hồng cầu được báo cáo là cao gấp 160 lần so với trong huyết tương, trong khi nồng độ kali trong hồng cầu chỉ cao gấp 23 lần [</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FF10147E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trích dẫn19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> ]. Chỉ cần 0,1% hồng cầu bị tan máu trong mẫu máu cũng có thể làm tăng hoạt động của LDH lên ít nhất 18% [</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FF10147E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trích dẫn35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> ]. Vì vậy, có mối tương quan rõ ràng giữa mức độ tan máu nhẹ trong các mẫu máu được vận chuyển và việc vận chuyển PTS, điều này phù hợp với kết luận của Kapoula et al. [</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FF10147E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trích dẫn9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> ]. Để ngăn ngừa hiện tượng tan máu nhẹ này, cần phải kiểm soát chất lượng của PTS, chẳng hạn như tiêu chuẩn fHb cao tới 9 mmol/L khi mua PTS mới cho các phòng thí nghiệm trong các cuộc đấu thầu công khai của Hoa Kỳ.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bốn nghiên cứu trước đây đã chỉ ra rằng hiện tượng tan máu có thể bị ảnh hưởng bởi tốc độ PTS, khoảng cách PTS, sự bảo vệ của mẫu máu và các đặc điểm khác của PTS [</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FF10147E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trích dẫn10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> ,</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FF10147E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trích dẫn19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> ,</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FF10147E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trích dẫn30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> ,</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FF10147E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trích dẫn37</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> ]. Một trong những nghiên cứu này cho thấy các mẫu máu dễ bị tan máu hơn trong giai đoạn 'khoảng cách xa và tốc độ cao' so với giai đoạn 'khoảng cách ngắn, tốc độ chậm' [</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FF10147E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trích dẫn30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> ]. Một nghiên cứu khác cho thấy việc sử dụng miếng lót cao su xốp có thể làm giảm tỷ lệ tan máu bằng cách giảm chuyển động và rung động của các mẫu trong ống [</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FF10147E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trích dẫn10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> ]. Hai nghiên cứu còn lại cho thấy các đặc điểm của PTS như loại, số khúc cua và tuyến đường vận chuyển có thể tạo ra các kết quả khác nhau [</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FF10147E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trích dẫn19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> ,</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="13"/>
+        <color rgb="FF10147E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trích dẫn37</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> ]. Phân tích nhóm phụ của chúng tôi cho thấy nồng độ LDH hoặc AST của các mẫu máu được vận chuyển bằng PTS cao hơn đáng kể so với mẫu máu được vận chuyển thủ công trong điều kiện PTS nhanh, PTS dài hoặc không có biện pháp bảo vệ. Do đó, có thể khuyến nghị nên sử dụng PTS ở tốc độ chậm, trên quãng đường ngắn và có biện pháp bảo vệ mẫu máu. Do sự đa dạng của các PTS và thiếu dữ liệu về số lượng khúc cua và tuyến đường vận chuyển, chúng tôi không tiến hành phân tích nhóm phụ về các đặc điểm này của PTS.</t>
+    </r>
+  </si>
+  <si>
+    <t>Một số hạn chế của nghiên cứu này cũng cần được đề cập. Số lượng nghiên cứu được đưa vào ít đồng nghĩa với việc cần thận trọng khi diễn giải kết quả về tỷ lệ tan máu, chỉ số tan máu và phân tích nhóm phụ của chúng. Hơn nữa, một số nghiên cứu không được đưa vào do thiếu dữ liệu cần thiết, điều này có thể dẫn đến sai lệch chọn lọc. Bên cạnh đó, vì số lượng khúc cua và tuyến đường vận chuyển không được báo cáo trong hầu hết các nghiên cứu, nên không thể khảo sát ảnh hưởng của các đặc điểm PTS này đến hiện tượng tan máu. Định nghĩa về tan máu quá rộng, không cho phép báo cáo kết quả đối với một số thành phần (AST, Folate hoặc LDH). Cuối cùng, các biến đổi tiền phân tích khác trong mẫu máu, chẳng hạn như đông máu, không được đưa vào nghiên cứu, nhưng vẫn có thể bị ảnh hưởng bởi PTS.</t>
+  </si>
+  <si>
+    <t>LDH</t>
+  </si>
+  <si>
+    <t>PTS</t>
+  </si>
+  <si>
+    <t>Hạn chế</t>
+  </si>
+  <si>
+    <t>Do đó, việc mỗi bệnh viện xác nhận và giám sát hệ thống PTS của mình, chẳng hạn như sử dụng thiết bị ghi dữ liệu và áp dụng các tiêu chuẩn hoặc khuyến nghị về PTS, là điều hợp lý. Hơn nữa, chúng tôi tin rằng hệ thống PTS sẽ hoạt động tốt hơn ở tốc độ chậm, quãng đường ngắn và có sự bảo vệ cho các mẫu máu. Các thử nghiệm đối chứng ngẫu nhiên với cỡ mẫu lớn hơn và thiết kế chặt chẽ hơn nên được thực hiện trong tương lai để kiểm chứng những kết luận này.</t>
+  </si>
+  <si>
+    <t>Kết luận</t>
+  </si>
+  <si>
+    <t>Comparison of pneumatic tube system with manual transport for routine chemistry, hematology, coagulation and blood gas tests</t>
+  </si>
+  <si>
+    <t>https://www.degruyter.com/document/doi/10.1515/cclm-2016-1157/html</t>
+  </si>
+  <si>
+    <t>Alex Pupek và cs</t>
+  </si>
+  <si>
+    <t>Duplicate samples were delivered to the core laboratory manually by human courier or via the Swisslog PTS. Head-to-head comparisons of 48 routine chemistry, hematology, coagulation and blood gas laboratory tests, and three sample integrity indices were conducted on 41 healthy volunteers and 61 adult patients.</t>
+  </si>
+  <si>
+    <t>Các tiến bộ trong quy trình xử lý mẫu tại phòng xét nghiệm không ngừng phát triển; với trọng tâm là tốc độ và tính tự động hóa, các cải tiến này nhằm giảm bớt gánh nặng cho nhân viên y tế và đẩy nhanh thời gian trả kết quả, qua đó nâng cao chất lượng chăm sóc bệnh nhân. Việc liên tục đưa vào sử dụng các công nghệ mới đặt ra nguy cơ đổi mới vượt xa tốc độ cập nhật quy định, đặc biệt khi các quy trình hiện đại được triển khai mà thiếu sự kiểm toán nội bộ và đảm bảo chất lượng thích hợp. Do nhân viên phòng xét nghiệm thường chú trọng nhiều hơn đến việc tuân thủ quy trình trong giai đoạn phân tích, nên các giai đoạn ngoài phân tích của quy trình xét nghiệm lâm sàng—bao gồm xử lý, bảo quản và vận chuyển—thường bị bỏ qua và lại chính là nơi xảy ra phần lớn các sai sót [1]. Một số tiến bộ trong giai đoạn tiền phân tích có thể phản tác dụng nếu chúng gây ra những rủi ro quá mức đối với tính toàn vẹn của mẫu chỉ vì mục đích thuận tiện.
+Các hệ thống vận chuyển nhanh (RDS) đã trở thành yếu tố gần như thiết yếu tại các bệnh viện lớn, hiện đại, giúp vận chuyển nhanh chóng thuốc và các mẫu máu giữa nhiều trạm được bố trí tại các vị trí chiến lược. Hiện nay, RDS chủ yếu tồn tại dưới dạng hệ thống ống khí nén (PTS); trong đó, một mạng lưới các đường ống kín khí sẽ luân chuyển các ống chứa hình trụ giữa các trạm nhờ cơ chế điều biến áp suất khí. Tùy thuộc vào loại hệ thống PTS và lộ trình vận chuyển, các mẫu vật có thể được chuyển đến đích một cách an toàn chỉ trong vài giây sau khi hệ thống được kích hoạt. PTS giúp mở rộng khả năng tiếp cận các thiết bị xét nghiệm trọng yếu và mang lại sự tiện lợi không kém gì các trạm xét nghiệm tại chỗ (point-of-care testing) [2]; Chúng cũng loại bỏ nhu cầu giám sát của con người trong quá trình vận chuyển mẫu. Nhờ đó, hệ thống vận chuyển bằng khí nén (PTS) trở thành một phần bổ sung thiết yếu cho giai đoạn tiền xét nghiệm: giúp chuyển mẫu nhanh chóng đến các phòng xét nghiệm trung tâm của bệnh viện, đồng thời giảm bớt gánh nặng vận chuyển thủ công và tránh được chi phí liên quan đến các hoạt động xét nghiệm tại điểm chăm sóc (POCT).
+Giai đoạn tiền phân tích là một thành phần chính trong thước đo cơ bản về chất lượng hoạt động của phòng xét nghiệm: thời gian hoàn thành xét nghiệm (TAT). Trong bối cảnh lâm sàng, TAT được định nghĩa là khoảng thời gian tính từ lúc có yêu cầu thực hiện một xét nghiệm cụ thể cho đến khi có kết quả; khi TAT vượt quá giới hạn chấp nhận được của cơ sở y tế, đó là tín hiệu cho thấy cần phải phân tích và cải thiện tất cả các giai đoạn của quy trình xét nghiệm [3]. TAT đối với các xét nghiệm máu đã giảm đáng kể nhờ sự ra đời của hệ thống vận chuyển bằng ống khí nén (PTS); cụ thể, việc triển khai PTS giúp giảm thời gian hoàn thành xét nghiệm trung bình từ 16%–24%, và con số này lên tới 33%–42% khi kết hợp với hệ thống quản lý y lệnh của bác sĩ trên máy tính [4, 5]. Rõ ràng là phương thức vận chuyển bằng ống khí nén, với khả năng rút ngắn TAT cho các kết quả có giá trị chẩn đoán, có thể cải thiện đáng kể nhiều khía cạnh trong công tác chăm sóc bệnh nhân. Mặc dù các tài liệu chuyên môn đều thống nhất rằng PTS giúp rút ngắn TAT, nhưng việc triển khai và nghiên cứu rộng rãi hệ thống này lại dẫn đến những kết quả không đồng nhất, thậm chí mâu thuẫn nhau về các chỉ số xét nghiệm, qua đó làm gia tăng lo ngại về tính toàn vẹn của mẫu bệnh phẩm.
+Khi các mẫu máu được vận chuyển qua hệ thống vận chuyển bằng khí nén (PTS), chúng phải chịu tác động của nhiều lực bên ngoài trong suốt quá trình di chuyển. Bên cạnh sự rung lắc và xáo trộn mạnh trên đường đi, ống chứa mẫu còn chịu những đợt gia tốc đáng kể, đặc biệt là tại thời điểm bắt đầu và kết thúc hành trình. Việc thay đổi hướng di chuyển trong quá trình vận chuyển bằng PTS khiến mẫu máu chịu tác động của dòng chảy rối, ứng suất cắt, cũng như làm gia tăng sự tương tác giữa các tế bào với nhau và giữa tế bào với bề mặt ống chứa mẫu [6, 7]. Những yếu tố này được cho là có ảnh hưởng đến tính toàn vẹn của mẫu, đồng thời gây ra tình trạng suy giảm chức năng tiểu cầu, tăng mức độ tan máu và kéo theo sự gia tăng nồng độ kali cũng như lactate dehydrogenase, v.v. [8, 9]. Ngoài ra, quá trình cân bằng và hòa trộn nhanh chóng của mẫu trong khi vận chuyển còn làm trầm trọng thêm tác động của việc nhiễm không khí từ môi trường – một nguyên nhân được ghi nhận gây ra sự sai lệch trong kết quả xét nghiệm khí máu [10–12]. Ngay cả một lượng rất nhỏ bọt khí trong mẫu cũng có thể dẫn đến sai lệch kết quả xét nghiệm khí máu, đặc biệt là đối với chỉ số pO2 [13].
+Do mỗi hệ thống vận chuyển bằng khí nén (PTS) đều được lắp đặt và cấu hình riêng biệt tùy theo từng cơ sở y tế, các bệnh viện cần tự đánh giá độ tin cậy của hệ thống PTS mà mình sử dụng; sự thiếu thống nhất trong các nghiên cứu trước đây càng củng cố thêm cho nhận định này. Mục tiêu của nghiên cứu này là thực hiện đánh giá nội bộ hệ thống PTS thông qua việc so sánh kết quả của 48 loại xét nghiệm (bao gồm hóa sinh, huyết học, đông máu và khí máu) trên các mẫu bệnh phẩm song song được vận chuyển theo hai phương thức: thủ công và bằng hệ thống PTS. Việc đánh giá và xác nhận này hướng tới các mục tiêu: khai thác tối đa hiệu quả của hệ thống PTS đối với nhiều loại xét nghiệm được chỉ định bởi phòng lấy mẫu máu, đơn vị hồi sức tích cực (ICU) và đơn vị hồi sức tích cực sơ sinh (NICU); giảm bớt gánh nặng công việc cho nhân viên phòng xét nghiệm nhờ loại bỏ nhu cầu vận chuyển mẫu thủ công; đáp ứng các yêu cầu từ cơ quan kiểm định chất lượng xét nghiệm cấp tỉnh cũng như các khuyến nghị trong những nghiên cứu trước đây về PTS [14]; rút ngắn thời gian trả kết quả (TAT); và nâng cao hiệu quả chăm sóc bệnh nhân bằng cách cung cấp cho bác sĩ lâm sàng các kết quả xét nghiệm chất lượng cao một cách nhanh chóng hơn.
+Gần đây, các thiết bị ghi dữ liệu tiên tiến đã được sử dụng để giám sát trực tiếp lực gia tốc, nhiệt độ, độ ẩm và áp suất không khí trong quá trình vận chuyển bằng hệ thống vận chuyển khí nén (PTS), cũng như đánh giá tác động của các yếu tố này đối với tính toàn vẹn của mẫu máu [15, 16]. Các mức lực gia tốc khác nhau tăng dần theo thời gian, tốc độ và quãng đường vận chuyển, dẫn đến việc nhiều chỉ số đông máu ROTEM® bị ảnh hưởng hơn, mặc dù tất cả các kết quả đều được đánh giá là chấp nhận được về mặt lâm sàng [17]. Trong nghiên cứu này, chúng tôi áp dụng phương pháp xét nghiệm mẫu phân đôi (split-sample testing) để khảo sát tác động của PTS đối với các giá trị xét nghiệm cuối cùng và tính toàn vẹn của mẫu—bao gồm chỉ số tan máu cũng như các thành phần nội bào hồng cầu (kali, lactate dehydrogenase và aspartate aminotransferase)—tương tự như cách tiếp cận trong các nghiên cứu nêu trên [15, 16].</t>
+  </si>
+  <si>
+    <t>Nghiên cứu bao gồm 56 cặp mẫu dùng cho phân tích huyết học và hóa sinh. Các cặp mẫu máu từ những bệnh nhân thực hiện quy trình thăm khám tiền phẫu đã được chọn ngẫu nhiên tại phòng lấy mẫu trong khoảng thời gian từ tháng 11 năm 2016 đến tháng 12 năm 2016, không xét đến chẩn đoán bệnh. Độ tuổi trung vị (khoảng giá trị) là 48 (22–87) tuổi; tỷ lệ nữ/nam là 37/19. Việc lấy mẫu máu được thực hiện bởi các nhân viên lấy mẫu đã qua đào tạo bài bản. Mẫu được thu thập vào 2 ống nhựa chân không chứa K2EDTA (Mã số 367856; BD Medical Systems, Franklin Lakes, NJ, USA) và 2 ống nhựa chân không tách huyết thanh (Mã số 367955; BD Medical Systems, Franklin Lakes, NJ, USA) từ cùng một lần chọc kim lấy máu tĩnh mạch. Các chỉ số xét nghiệm được đo đạc dựa trên lượng máu dư còn lại (vốn sẽ bị loại bỏ). Nghiên cứu này đã được Hội đồng Đánh giá Thể chế tại Trung tâm Y tế Đại học Công giáo Daegu (DCUMC) phê duyệt.
+Hệ thống vận chuyển mẫu bằng khí nén (PTS) được lắp đặt tại DCUMC là hệ thống một chiều, vận hành bằng máy tính và sử dụng đường ống có đường kính 2,5 cm (Tempus600®, TIMEDICO A/S, Đan Mạch). Các ống mẫu (gồm một ống chứa K2EDTA và một ống tách huyết thanh) được vận chuyển qua hệ thống PTS này. Các ống mẫu tương ứng khác được nhân viên phòng xét nghiệm vận chuyển thủ công. Tại DCUMC, phòng xét nghiệm lâm sàng nằm ở tầng 5, trong khi phòng lấy mẫu nằm ở tầng 1. Khoảng cách giữa hai trạm của hệ thống PTS là khoảng 347 feet (106 mét). Hệ thống hoạt động với tốc độ 7–10 m/s và sử dụng các trạm trung chuyển có chức năng tăng tốc cũng như giảm tốc cho mẫu trong quá trình di chuyển giữa các phân đoạn của hệ thống.
+3. Các thông số phân tích
+4. Phương pháp thống kê</t>
+  </si>
+  <si>
+    <t>A-Jin Lee và cs</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">median values of chemistry parameters were not significantly different except for 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>AST (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <i/>
         <sz val="12"/>
-        <color rgb="FF1F1F1F"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Georgia"/>
         <family val="1"/>
       </rPr>
@@ -100,18 +403,21 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="12"/>
-        <color rgb="FF1F1F1F"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Georgia"/>
         <family val="1"/>
       </rPr>
-      <t> = 0.000), LDH (</t>
-    </r>
-    <r>
-      <rPr>
+      <t> = 0.000), 
+LDH (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <i/>
         <sz val="12"/>
-        <color rgb="FF1F1F1F"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Georgia"/>
         <family val="1"/>
       </rPr>
@@ -119,8 +425,9 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="12"/>
-        <color rgb="FF1F1F1F"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Georgia"/>
         <family val="1"/>
       </rPr>
@@ -128,9 +435,10 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <i/>
         <sz val="12"/>
-        <color rgb="FF1F1F1F"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Georgia"/>
         <family val="1"/>
       </rPr>
@@ -138,8 +446,9 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="12"/>
-        <color rgb="FF1F1F1F"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Georgia"/>
         <family val="1"/>
       </rPr>
@@ -147,29 +456,209 @@
     </r>
   </si>
   <si>
-    <t>Trong quá trình vận chuyển mẫu trong PTS, mẫu máu phải chịu tốc độ cao, gia tốc và giảm tốc nhanh [3] 
-Người ta đã báo cáo rằng giai đoạn tăng tốc và giảm tốc trong quá trình vận chuyển PTS có thể ảnh hưởng đến chất lượng mẫu và dẫn đến tan máu [14] , [15] , [16] 
-mức độ tan máu, LDH huyết tương và mức độ K không khác biệt đáng kể ở các mẫu ly tâm được vận chuyển bằng PTS và người mang, bất kể tốc độ và khoảng cách trong nghiên cứu trước đó [17]
-https://onlinelibrary.wiley.com/doi/epdf/10.1002/jcla.21484. Những khác biệt này có thể là do các nhà sản xuất PTS khác nhau, chiều dài PTS khác nhau, tốc độ khác nhau và phương pháp lắp đặt khác nhau. 
-Những thay đổi này chủ yếu có thể dẫn đến sự gia tăng nồng độ LDH và nồng độ kali  [4] , [5] 
-https://academic.oup.com/clinchem/article-abstract/17/12/1160/5675904?redirectedFrom=fulltext&amp;login=false
-https://sci-hub.vn/10.1258/000456304323019631
-Mặt khác, người ta đã chứng minh rằng PTS không ảnh hưởng đến các mẫu và mức độ K không cho thấy sự khác biệt đáng kể [9] 
-Những khác biệt này có thể là do các nhà sản xuất PTS khác nhau, chiều dài PTS khác nhau, tốc độ khác nhau và phương pháp lắp đặt khác nhau. Trong nghiên cứu hiện tại, tốc độ vận chuyển là 10 m/s, nhanh hơn tốc độ của nghiên cứu trước đó. Giai đoạn tăng tốc và giảm tốc thông qua hệ thống PTS có thể dẫn đến tan máu và làm tăng các thông số hóa học liên quan đến tổn thương hồng cầu . Tuy nhiên, hầu hết các giá trị AST, LDH và chỉ số tan máu đều nằm trong khoảng tin cậy 95% của sự khác biệt trung bình. Những giá trị này không thể ảnh hưởng đến quyết định lâm sàng quan trọng. Tuy nhiên, nếu kết quả cao bất ngờ, những khác biệt này có thể bắt nguồn từ việc vận chuyển bằng PTS.
+    <r>
+      <t xml:space="preserve">Hệ thống vận chuyển bằng khí nén (PTS) không gây ảnh hưởng đến các chỉ số tán huyết, tăng lipid máu hay vàng da của mẫu (tất cả đều có p &lt; 0,05). 
+alkaline phosphatase, bilirubin toàn phần và hemoglobin cho thấy sự khác biệt có ý nghĩa thống kê (lần lượt là p = 0,009; 0,027 và 0,012), nhưng tất cả đều có độ lệch trung bình rất thấp, dao động từ 0,01% đến 2%. 
+Tất cả những khác biệt quan sát được ở 48 xét nghiệm này đều không có ý nghĩa về mặt lâm sàng.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--&gt; AST, LDH, Kali ko có sự khác biệt</t>
+    </r>
+  </si>
+  <si>
+    <t>Trong nghiên cứu này, chúng tôi đánh giá tác động của hệ thống vận chuyển mẫu bằng khí nén (PTS) mới đối với các chỉ số huyết học và hóa sinh. Trong quá trình vận chuyển qua PTS, các mẫu máu phải chịu tác động của tốc độ cao cũng như sự gia tốc và giảm tốc đột ngột [3]. Điều này có thể làm tăng nguy cơ tan máu, đồng thời ảnh hưởng đến chất lượng mẫu và kết quả xét nghiệm. Do đó, việc xác nhận độ ổn định của mẫu khi vận chuyển qua PTS là yếu tố then chốt để đảm bảo quy trình phân tích chính xác và kết quả xét nghiệm tin cậy. Trong nghiên cứu này, chúng tôi đã so sánh kết quả thu được từ quy trình vận chuyển bằng PTS với kết quả thu được từ quy trình vận chuyển thủ công.
+Hầu hết các chỉ số sinh hóa không cho thấy sự khác biệt có ý nghĩa thống kê. Các chỉ số liên quan đến tan máu, bao gồm LDH, chỉ số tan máu và AST, cho thấy sự khác biệt có ý nghĩa thống kê. Kết quả từ các mẫu vận chuyển bằng hệ thống vận chuyển khí nén (PTS) có xu hướng cao hơn so với kết quả từ các mẫu được vận chuyển thủ công. 
+Giá trị trung bình của sự khác biệt giữa phương pháp PTS và phương pháp vận chuyển thủ công đều lớn hơn không đối với các chỉ số AST, LDH, K và chỉ số tan máu.
+Tuy nhiên, biểu đồ Bland-Altman cho các chỉ số này cho thấy một số ít giá trị ngoại lai nằm trong khoảng tham chiếu, điều này có thể do tình trạng cụ thể của từng cá nhân. Không có giá trị ngoại lai nào đáng kể đến mức ảnh hưởng đến việc đánh giá và xử trí lâm sàng. Những khác biệt đối với AST, LDH, K và chỉ số tan máu này có thể dẫn đến sai số hệ thống. 
+Các nghiên cứu trước đây đã chỉ ra rằng giai đoạn tăng tốc và giảm tốc trong quá trình vận chuyển bằng PTS có thể ảnh hưởng đến chất lượng mẫu và gây ra hiện tượng tan máu [14–16]. Những thay đổi này chủ yếu dẫn đến sự gia tăng nồng độ LDH và kali [3–5]. Mặt khác, cũng có nghiên cứu chứng minh rằng PTS không ảnh hưởng đến mẫu và nồng độ K không cho thấy sự khác biệt đáng kể [9]. Mặc dù việc vận chuyển bằng PTS có thể ảnh hưởng nghiêm trọng đến các xét nghiệm thường quy trên mẫu chưa ly tâm, nhưng mức độ tan máu cũng như nồng độ LDH và K trong huyết tương lại không có sự khác biệt đáng kể giữa mẫu đã ly tâm được vận chuyển bằng PTS và mẫu được vận chuyển thủ công, bất kể tốc độ hay khoảng cách trong một nghiên cứu trước đó [17]. Những khác biệt này có thể do sự khác biệt về nhà sản xuất PTS, chiều dài hệ thống, tốc độ vận chuyển và phương pháp lắp đặt. 
+Trong nghiên cứu hiện tại, tốc độ vận chuyển là 10 m/s, nhanh hơn so với tốc độ trong nghiên cứu trước đó. Các giai đoạn tăng tốc và giảm tốc trong hệ thống PTS có thể gây ra tan máu và làm tăng các chỉ số sinh hóa liên quan đến tổn thương hồng cầu. Tuy nhiên, hầu hết các giá trị của AST, LDH và chỉ số tan máu đều nằm trong khoảng tin cậy 95% của giá trị trung bình khác biệt. Những giá trị này không ảnh hưởng đến các quyết định lâm sàng quan trọng. Dù vậy, nếu kết quả cao bất thường, thì những khác biệt này có thể bắt nguồn từ quá trình vận chuyển bằng PTS.
 Nghiên cứu này có một số hạn chế. Hạn chế đầu tiên là quy mô mẫu nhỏ . Một hạn chế khác là phần lớn kết quả xét nghiệm nằm trong phạm vi bình thường.
  Các thông số hóa học bao gồm AST, LDH và chỉ số tán huyết, vốn bị ảnh hưởng bởi hiện tượng tán huyết, có xu hướng cho kết quả cao hơn ở các mẫu được vận chuyển qua hệ thống PTS. Tất cả các phòng thí nghiệm nên xác nhận tính ổn định của kết quả từ các mẫu tùy thuộc vào phương pháp vận chuyển.</t>
   </si>
   <si>
-    <t>Năm nghiên cứu [Trích dẫn16 ,Trích dẫn18 ,Trích dẫn24 ,Trích dẫn26 ,Trích dẫn36 ] đã điều tra tác động của PTS lên chỉ số tán huyết của các mẫu máu. Phân tích tổng hợp của chúng tôi cho thấy chỉ số tán huyết không khác biệt đáng kể giữa nhóm PTS (213 mẫu máu) và nhóm vận chuyển thủ công (213 mẫu máu) (SMD = 0,19, 95% CI = −0,00 đến 0,38, p  = 0,06, I 2 = 0,00%) (Hình 2(B)Phân tích nhóm phụ cho thấy rằng phương pháp PTS và vận chuyển thủ công không khác biệt đáng kể giữa các nhóm phụ về tốc độ PTS và bảo vệ mẫu máu (tất cả p  &gt; 0,05).
-21 bài báo [Trích dẫn5 ,Trích dẫn10 ,Trích dẫn11 ,Trích dẫn13 ,Trích dẫn15–20 ,Trích dẫn23 ,Trích dẫn24 ,Trích dẫn26 ,Trích dẫn28–35 ] bao gồm 1219 mẫu trong nhóm PTS và 1219 mẫu trong nhóm vận chuyển thủ công đã báo cáo mức LDH. Thử nghiệm tính không đồng nhất cho thấy sự hiện diện của tính không đồng nhất đáng kể giữa các nghiên cứu này ( I² = 61,8%, p  &lt; 0,001). Phân tích tổng hợp của chúng tôi cho thấy mức LDH trong các mẫu máu cao hơn ở những người được vận chuyển bằng PTS so với những người được vận chuyển thủ công (SMD = 0,20, 95% CI = 0,06 đến 0,34, p  = 0,01) (Hình 3(B)Phân tích nhóm phụ cho thấy nồng độ LDH cao hơn rõ rệt ở nhóm PTS so với nhóm vận chuyển bằng tay khi tốc độ PTS ≥ 6 m/s (SMD = 0,31, 95% CI = 0,04 đến 0,58, p =  0,02, I² = 70,70%), trong khi không có sự khác biệt nào được quan sát giữa hai nhóm khi tốc độ &lt; 6 m / s (SMD = 0,13, 95% CI = −0,09 đến 0,35, p  = 0,25, I² = 66,90%). Trong khi đó, đối với quãng đường vận chuyển dài (≥250 m), có sự khác biệt đáng kể giữa nhóm vận chuyển bằng thiết bị y tế tự động (PTS) và nhóm vận chuyển thủ công (SMD = 0,30, khoảng tin cậy 95% = 0,04 đến 0,56, p =  0,03, I² = 64,80%), còn đối với quãng đường ngắn (&lt;250 m) thì không có sự khác biệt nào (SMD = 0,10, khoảng tin cậy 95% = −0,11 đến 0,31, p =  0,34, I² = 71,60%). Nhóm PTS và nhóm vận chuyển thủ công khác biệt đáng kể bất kể mẫu máu có được bảo vệ hay không (tất cả p  &lt; 0,05).
-Nghiên cứu của chúng tôi bao gồm 15 nghiên cứu [Trích dẫn5 ,Trích dẫn10 ,Trích dẫn11 ,Trích dẫn13–15 ,Trích dẫn23–26 ,Trích dẫn28 ,Trích dẫn29 ,Trích dẫn31 ,Trích dẫn32 ,Trích dẫn35 ] trong đó có sẵn mức AST, bao gồm 919 mẫu trong nhóm PTS và 919 mẫu trong nhóm vận chuyển thủ công. Thử nghiệm tính không đồng nhất cho thấy I 2 = 35,70% và p  = 0,08, cho thấy không có sự không đồng nhất đáng kể. Mức AST không khác biệt đáng kể giữa hai nhóm (SMD = 0,04, 95% CI = −0,08 đến 0,17, p = 0,48) (Hình 4(B)Phân tích nhóm phụ cho thấy rằng khi khoảng cách nhỏ hơn 250 m, nồng độ AST không khác biệt đáng kể giữa nhóm vận chuyển bằng xe tự động (PTS) và nhóm vận chuyển thủ công (SMD = −0,04, 95% CI = −0,29 đến 0,21, p =  0,77, I² = 67,10%), trong khi có sự khác biệt đáng kể đối với khoảng cách dài hơn (SMD = 0,18, 95% CI = 0,28 đến 0,33, p  = 0,02, I² = 0,00%). Trong nhóm được bảo vệ, nồng độ AST cao hơn đáng kể đối với các mẫu máu được vận chuyển bằng xe tự động so với các mẫu được vận chuyển thủ công (SMD = 0,05, 95% CI = −0,18 đến 0,27, p  = 0,70, I² = 67,20%). Tuy nhiên, không có sự khác biệt đáng kể giữa các nhóm về mức AST ở nhóm không được bảo vệ (SMD = 0,14, 95% CI = 0,01 đến 0,26, p  = 0,03, I² = 0,00%). Không có sự khác biệt rõ ràng nào được xác định giữa hai nhóm theo tốc độ PTS (tất cả p  &gt; 0,05).</t>
-  </si>
-  <si>
-    <t>KQ1 ảnh hưởng chỉ số tan máu</t>
-  </si>
-  <si>
-    <r>
-      <t>PTS không ảnh hưởng đến chỉ số tan máu của mẫu máu, điều này phù hợp với kết luận của Koessler et al. [</t>
+    <r>
+      <t xml:space="preserve">Năm nghiên cứu [Trích dẫn16 ,Trích dẫn18 ,Trích dẫn24 ,Trích dẫn26 ,Trích dẫn36 ] đã điều tra tác động của PTS lên chỉ số tán huyết của các mẫu máu. Phân tích tổng hợp của chúng tôi cho thấy chỉ số tán huyết không khác biệt đáng kể giữa nhóm PTS (213 mẫu máu) và nhóm vận chuyển thủ công (213 mẫu máu) (SMD = 0,19, 95% CI = −0,00 đến 0,38, p  = 0,06, I 2 = 0,00%) (Hình 2(B)Phân tích nhóm phụ cho thấy rằng phương pháp PTS và vận chuyển thủ công không khác biệt đáng kể giữa các nhóm phụ về tốc độ PTS và bảo vệ mẫu máu (tất cả p  &gt; 0,05).
+21 bài báo [Trích dẫn5 ,Trích dẫn10 ,Trích dẫn11 ,Trích dẫn13 ,Trích dẫn15–20 ,Trích dẫn23 ,Trích dẫn24 ,Trích dẫn26 ,Trích dẫn28–35 ] bao gồm 1219 mẫu trong nhóm PTS và 1219 mẫu trong nhóm vận chuyển thủ công đã báo cáo mức LDH. Thử nghiệm tính không đồng nhất cho thấy sự hiện diện của tính không đồng nhất đáng kể giữa các nghiên cứu này ( I² = 61,8%, p  &lt; 0,001). 
+Phân tích tổng hợp của chúng tôi cho thấy </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mức LDH trong các mẫu máu cao hơn ở những người được vận chuyển bằng PTS so với những người được vận chuyển thủ công</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (SMD = 0,20, 95% CI = 0,06 đến 0,34, p  = 0,01) (Hình 3(B)Phân tích nhóm phụ cho thấy nồng độ LDH cao hơn rõ rệt ở nhóm PTS so với nhóm vận chuyển bằng tay khi tốc độ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PTS ≥ 6 m/s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (SMD = 0,31, 95% CI = 0,04 đến 0,58, p =  0,02, I² = 70,70%), trong khi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không có sự khác biệt nào được quan sát giữa hai nhóm khi tốc độ &lt; 6 m / s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (SMD = 0,13, 95% CI = −0,09 đến 0,35, p  = 0,25, I² = 66,90%). Trong khi đó, đối với</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> quãng đường vận chuyển dài (≥250 m), có sự khác biệt đáng kể</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> giữa nhóm vận chuyển bằng thiết bị y tế tự động (PTS) và nhóm vận chuyển thủ công (SMD = 0,30, khoảng tin cậy 95% = 0,04 đến 0,56, p =  0,03, I² = 64,80%), còn đối với quãng đường ngắn (&lt;250 m) thì không có sự khác biệt nào (SMD = 0,10, khoảng tin cậy 95% = −0,11 đến 0,31, p =  0,34, I² = 71,60%). Nhóm PTS và nhóm vận chuyển thủ công </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>khác biệt đáng kể bất kể mẫu máu có được bảo vệ hay không</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (tất cả p  &lt; 0,05).
+Nghiên cứu của chúng tôi bao gồm 15 nghiên cứu [Trích dẫn5 ,Trích dẫn10 ,Trích dẫn11 ,Trích dẫn13–15 ,Trích dẫn23–26 ,Trích dẫn28 ,Trích dẫn29 ,Trích dẫn31 ,Trích dẫn32 ,Trích dẫn35 ] 
+trong đó có sẵn mức AST, bao gồm 919 mẫu trong nhóm PTS và 919 mẫu trong nhóm vận chuyển thủ công. Thử nghiệm tính không đồng nhất cho thấy I 2 = 35,70% và p  = 0,08, cho thấy không có sự không đồng nhất đáng kể. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mức AST không khác biệt đáng kể</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> giữa hai nhóm (SMD = 0,04, 95% CI = −0,08 đến 0,17, p = 0,48) (Hình 4(B)Phân tích nhóm phụ cho thấy rằng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>khi khoảng cách nhỏ hơn 250 m, nồng độ AST không khác biệt đáng kể</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> giữa nhóm vận chuyển bằng xe tự động (PTS) và nhóm vận chuyển thủ công (SMD = −0,04, 95% CI = −0,29 đến 0,21, p =  0,77, I² = 67,10%), trong khi có sự khác biệt đáng kể đối với khoảng cách dài hơn (SMD = 0,18, 95% CI = 0,28 đến 0,33, p  = 0,02, I² = 0,00%). Trong nhóm được bảo vệ, nồng độ AST cao hơn đáng kể đối với các mẫu máu được vận chuyển bằng xe tự động so với các mẫu được vận chuyển thủ công (SMD = 0,05, 95% CI = −0,18 đến 0,27, p  = 0,70, I² = 67,20%). Tuy nhiên, không có sự khác biệt đáng kể giữa các nhóm về mức AST ở nhóm không được bảo vệ (SMD = 0,14, 95% CI = 0,01 đến 0,26, p  = 0,03, I² = 0,00%). Không có sự khác biệt rõ ràng nào được xác định giữa hai nhóm theo tốc độ PTS (tất cả p  &gt; 0,05).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PTS không ảnh hưởng đến chỉ số tan máu của mẫu máu,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> điều này phù hợp với kết luận của Koessler et al. [</t>
     </r>
     <r>
       <rPr>
@@ -228,275 +717,13 @@
       </rPr>
       <t> ]. báo cáo rằng chỉ số tan máu cao hơn đối với PTS so với vận chuyển thủ công, điều này có thể là do tốc độ PTS cao trong nghiên cứu đó làm tăng chỉ số tan máu do tổn thương hồng cầu. Sự khác biệt về đặc điểm của PTS giữa các nghiên cứu này cũng có thể góp phần vào sự khác biệt được quan sát thấy.</t>
     </r>
-  </si>
-  <si>
-    <t>KQ2 ảnh hưởng chỉ số hóa sinh</t>
-  </si>
-  <si>
-    <t>không tìm thấy tác động đáng kể của PTS lên hiện tượng tan máu đã được khẳng định thêm bằng việc không có sự khác biệt rõ rệt nào giữa các hợp chất hồng cầu như K, ALT và AST giữa các mẫu được vận chuyển bằng PTS hoặc bằng tay. Tương tự, Pupek et al. [Trích dẫn28 ] tin rằng việc sử dụng PTS không ảnh hưởng đến nồng độ K, ALT và AST trong mẫu máu. Kapoula et al. [Trích dẫn23 ] cũng báo cáo rằng phương thức vận chuyển không có tác động đáng kể đến các thông số huyết thanh đo được như nồng độ K và AST. Tuy nhiên, phân tích tổng hợp do Kapoula et al. thực hiện [Trích dẫn9 ] đã mang lại kết quả có ý nghĩa thống kê đối với K và AST. Các nguyên nhân có thể dẫn đến sự khác biệt này như sau: (1) các mẫu máu được phân tích trong nghiên cứu của họ được lấy từ một quy trình chọc tĩnh mạch duy nhất, nhưng các giá trị cơ bản cho các mẫu máu ghép đôi được phân tích song song là tương đương, và chúng cũng được đưa vào nghiên cứu của chúng tôi; (2) Kapoula et al. đã sử dụng sự khác biệt trung bình làm kích thước hiệu ứng, khác với việc chúng tôi sử dụng SMD; và (3) cuối cùng, phân tích tổng hợp của chúng tôi gần đây hơn và bao gồm nhiều bài báo tạp chí hơn so với của Kapoula et al.</t>
-  </si>
-  <si>
-    <r>
-      <t>Một phát hiện đặc biệt thú vị trong nghiên cứu của chúng tôi là các mẫu máu được vận chuyển bằng hệ thống PTS có nồng độ LDH cao hơn so với các mẫu được vận chuyển thủ công (với khoảng tin cậy 95% từ 0,06 đến 0,34). Chúng tôi nghi ngờ rằng chỉ có LDH từ các mẫu được vận chuyển bằng hệ thống PTS cho thấy sự khác biệt đáng kể do nồng độ LDH cao hơn ngưỡng nhạy cảm của xét nghiệm.</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FF10147E"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trích dẫn35</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> ]. Nồng độ LDH trong hồng cầu được báo cáo là cao gấp 160 lần so với trong huyết tương, trong khi nồng độ kali trong hồng cầu chỉ cao gấp 23 lần [</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FF10147E"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trích dẫn19</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> ]. Chỉ cần 0,1% hồng cầu bị tan máu trong mẫu máu cũng có thể làm tăng hoạt động của LDH lên ít nhất 18% [</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FF10147E"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trích dẫn35</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> ]. Vì vậy, có mối tương quan rõ ràng giữa mức độ tan máu nhẹ trong các mẫu máu được vận chuyển và việc vận chuyển PTS, điều này phù hợp với kết luận của Kapoula et al. [</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FF10147E"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trích dẫn9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> ]. Để ngăn ngừa hiện tượng tan máu nhẹ này, cần phải kiểm soát chất lượng của PTS, chẳng hạn như tiêu chuẩn fHb cao tới 9 mmol/L khi mua PTS mới cho các phòng thí nghiệm trong các cuộc đấu thầu công khai của Hoa Kỳ.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Bốn nghiên cứu trước đây đã chỉ ra rằng hiện tượng tan máu có thể bị ảnh hưởng bởi tốc độ PTS, khoảng cách PTS, sự bảo vệ của mẫu máu và các đặc điểm khác của PTS [</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FF10147E"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trích dẫn10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> ,</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FF10147E"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trích dẫn19</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> ,</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FF10147E"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trích dẫn30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> ,</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FF10147E"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trích dẫn37</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> ]. Một trong những nghiên cứu này cho thấy các mẫu máu dễ bị tan máu hơn trong giai đoạn 'khoảng cách xa và tốc độ cao' so với giai đoạn 'khoảng cách ngắn, tốc độ chậm' [</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FF10147E"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trích dẫn30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> ]. Một nghiên cứu khác cho thấy việc sử dụng miếng lót cao su xốp có thể làm giảm tỷ lệ tan máu bằng cách giảm chuyển động và rung động của các mẫu trong ống [</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FF10147E"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trích dẫn10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> ]. Hai nghiên cứu còn lại cho thấy các đặc điểm của PTS như loại, số khúc cua và tuyến đường vận chuyển có thể tạo ra các kết quả khác nhau [</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FF10147E"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trích dẫn19</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> ,</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="13"/>
-        <color rgb="FF10147E"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trích dẫn37</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> ]. Phân tích nhóm phụ của chúng tôi cho thấy nồng độ LDH hoặc AST của các mẫu máu được vận chuyển bằng PTS cao hơn đáng kể so với mẫu máu được vận chuyển thủ công trong điều kiện PTS nhanh, PTS dài hoặc không có biện pháp bảo vệ. Do đó, có thể khuyến nghị nên sử dụng PTS ở tốc độ chậm, trên quãng đường ngắn và có biện pháp bảo vệ mẫu máu. Do sự đa dạng của các PTS và thiếu dữ liệu về số lượng khúc cua và tuyến đường vận chuyển, chúng tôi không tiến hành phân tích nhóm phụ về các đặc điểm này của PTS.</t>
-    </r>
-  </si>
-  <si>
-    <t>Một số hạn chế của nghiên cứu này cũng cần được đề cập. Số lượng nghiên cứu được đưa vào ít đồng nghĩa với việc cần thận trọng khi diễn giải kết quả về tỷ lệ tan máu, chỉ số tan máu và phân tích nhóm phụ của chúng. Hơn nữa, một số nghiên cứu không được đưa vào do thiếu dữ liệu cần thiết, điều này có thể dẫn đến sai lệch chọn lọc. Bên cạnh đó, vì số lượng khúc cua và tuyến đường vận chuyển không được báo cáo trong hầu hết các nghiên cứu, nên không thể khảo sát ảnh hưởng của các đặc điểm PTS này đến hiện tượng tan máu. Định nghĩa về tan máu quá rộng, không cho phép báo cáo kết quả đối với một số thành phần (AST, Folate hoặc LDH). Cuối cùng, các biến đổi tiền phân tích khác trong mẫu máu, chẳng hạn như đông máu, không được đưa vào nghiên cứu, nhưng vẫn có thể bị ảnh hưởng bởi PTS.</t>
-  </si>
-  <si>
-    <t>LDH</t>
-  </si>
-  <si>
-    <t>PTS</t>
-  </si>
-  <si>
-    <t>Hạn chế</t>
-  </si>
-  <si>
-    <t>Do đó, việc mỗi bệnh viện xác nhận và giám sát hệ thống PTS của mình, chẳng hạn như sử dụng thiết bị ghi dữ liệu và áp dụng các tiêu chuẩn hoặc khuyến nghị về PTS, là điều hợp lý. Hơn nữa, chúng tôi tin rằng hệ thống PTS sẽ hoạt động tốt hơn ở tốc độ chậm, quãng đường ngắn và có sự bảo vệ cho các mẫu máu. Các thử nghiệm đối chứng ngẫu nhiên với cỡ mẫu lớn hơn và thiết kế chặt chẽ hơn nên được thực hiện trong tương lai để kiểm chứng những kết luận này.</t>
-  </si>
-  <si>
-    <t>Kết luận</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -519,13 +746,6 @@
       <family val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="13"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
@@ -538,13 +758,57 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -563,22 +827,22 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -864,130 +1128,158 @@
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.42578125" style="2" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="2"/>
-    <col min="5" max="5" width="38.140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20" style="2" customWidth="1"/>
-    <col min="7" max="7" width="25.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="60.85546875" style="2" customWidth="1"/>
-    <col min="9" max="10" width="9.140625" style="2"/>
-    <col min="11" max="12" width="9.140625" style="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="2" width="11.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="1"/>
+    <col min="5" max="5" width="38.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="60.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="27.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5703125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:14" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="I1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>31</v>
+      <c r="L1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D3" s="1">
         <v>2021</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="H3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="L3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="6" t="s">
+      <c r="N3" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="75" x14ac:dyDescent="0.25">
-      <c r="G3" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>18</v>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2017</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" location="abstract"/>
+    <hyperlink ref="A3" r:id="rId1" location="abstract"/>
     <hyperlink ref="A4" r:id="rId2"/>
+    <hyperlink ref="A2" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId3"/>
+  <pageSetup orientation="landscape" r:id="rId4"/>
 </worksheet>
 </file>